--- a/output/pdf_financials_xlsx/GFG.xlsx
+++ b/output/pdf_financials_xlsx/GFG.xlsx
@@ -5162,43 +5162,43 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.0456</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.0456</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.0456</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.211649</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.294244</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.163601</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.659915</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.158593</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.40552</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.651107</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>3.156058</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>3.558454</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>3.598398</v>
       </c>
     </row>
     <row r="93">
@@ -9405,7 +9405,11 @@
           <t>Reserves (note 17)</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -13126,7 +13130,11 @@
           <t>Reserves (Note 16)</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
           <t>-</t>
@@ -15654,7 +15662,11 @@
           <t>Reserves (Note 18)</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E105" t="inlineStr">
         <is>
           <t>-</t>
@@ -17084,7 +17096,11 @@
           <t>Reserve (Note 18)</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr"/>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
           <t>-</t>
@@ -18577,7 +18593,11 @@
           <t>Reserve (Note 16)</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr"/>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E142" t="inlineStr">
         <is>
           <t>-</t>
@@ -21860,7 +21880,11 @@
           <t>Reserve (Note 17)</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr"/>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E183" t="inlineStr">
         <is>
           <t>-</t>
@@ -22749,7 +22773,11 @@
           <t>Reserve</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr"/>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E194" t="inlineStr">
         <is>
           <t>-</t>
@@ -23251,7 +23279,11 @@
           <t>Reserves (Note 4) 45,600</t>
         </is>
       </c>
-      <c r="D200" t="inlineStr"/>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
           <t>-</t>
@@ -24322,7 +24354,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D213" t="inlineStr"/>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E213" t="inlineStr">
         <is>
           <t>-</t>
@@ -24899,7 +24935,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D220" t="inlineStr"/>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E220" s="5" t="n">
         <v>0.0456</v>
       </c>
@@ -25818,7 +25858,11 @@
           <t>RESERVES (note 7) 45,600</t>
         </is>
       </c>
-      <c r="D231" t="inlineStr"/>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E231" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/GFG.xlsx
+++ b/output/pdf_financials_xlsx/GFG.xlsx
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0018</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -2023,10 +2023,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.117337</v>
+        <v>-0.119137</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.128742</v>
+        <v>-0.130542</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.117337</v>
+        <v>-0.119137</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.128742</v>
+        <v>-0.130542</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -2439,22 +2439,22 @@
         <v>0.01654</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>1.203468</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>5.135605</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>4.24877</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.561317</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>7.029509</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.605172</v>
       </c>
       <c r="K34" s="3" t="n">
         <v>1.227744</v>
@@ -2531,22 +2531,22 @@
         <v>0.01654</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>1.203468</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>5.135605</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>4.24877</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>1.561317</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>7.029509</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>1.605172</v>
       </c>
       <c r="K36" s="3" t="n">
         <v>1.227744</v>
@@ -3083,22 +3083,22 @@
         <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.240681</v>
+        <v>0.037213</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>5.200603</v>
+        <v>0.064998</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>4.339561</v>
+        <v>0.090791</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.641329</v>
+        <v>0.080012</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>7.115713</v>
+        <v>0.086204</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.703368</v>
+        <v>0.09819600000000001</v>
       </c>
       <c r="K48" s="3" t="n">
         <v>0.497222</v>
@@ -6889,13 +6889,13 @@
         </is>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.040785</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.040785</v>
       </c>
       <c r="N124" s="3" t="n">
-        <v>0</v>
+        <v>-0.042598</v>
       </c>
     </row>
     <row r="125">
@@ -6945,13 +6945,13 @@
         </is>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.040785</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.040785</v>
       </c>
       <c r="N125" s="3" t="n">
-        <v>0</v>
+        <v>-0.042598</v>
       </c>
     </row>
     <row r="126">
@@ -16539,7 +16539,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -21965,7 +21965,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -22856,7 +22856,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -25269,7 +25269,7 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E224" s="5" t="n">
@@ -28179,7 +28179,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D260" t="inlineStr"/>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E260" t="inlineStr">
         <is>
           <t>-</t>
@@ -40427,7 +40431,7 @@
       </c>
       <c r="D410" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E410" s="5" t="n">
@@ -42071,7 +42075,7 @@
       </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E430" s="5" t="n">
@@ -43288,7 +43292,7 @@
       </c>
       <c r="D445" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E445" t="inlineStr">

--- a/output/pdf_financials_xlsx/GFG.xlsx
+++ b/output/pdf_financials_xlsx/GFG.xlsx
@@ -5543,13 +5543,13 @@
         </is>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.031245</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.031245</v>
       </c>
       <c r="N100" s="3" t="n">
-        <v>0</v>
+        <v>0.031245</v>
       </c>
     </row>
     <row r="101">
@@ -26423,7 +26423,11 @@
           <t>Depreciation - right-of-use asset</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E238" t="inlineStr">
         <is>
           <t>-</t>
